--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>23862.63</v>
+        <v>23758.03</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>53111.95</v>
+        <v>53610.1</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>13958.77</v>
+        <v>14098.55</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>46016.52</v>
+        <v>46114.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -755,6 +755,372 @@
         <v>46114.6</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1178-45-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>INVERSIONES MTEA SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.366.361-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>183957.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1057439-4946-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.935.610-k</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>12669.88</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1305532-62-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>VIVANET</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>14925.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1057439-5370-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.935.610-k</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>3128.84</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2446-925-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>VIVANET</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>14473.68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1305532-73-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>VIVANET</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>12914.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ITRAVEL -  TRANSPORTE PRIVADO DE PASAJEROS</t>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1119,6 +1119,189 @@
       </c>
       <c r="M11" s="2" t="n">
         <v>12914.61</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1057439-5612-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.935.610-k</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>69525.53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>931-165-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>JOSUE MANUEL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.370.023-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>20647.27</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>931-167-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>9912.15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/coquimbo.xlsx
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
